--- a/Bases_de_Dados/FootyStats/Netherlands Eredivisie_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Netherlands Eredivisie_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP219"/>
+  <dimension ref="A1:BP221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ3" t="n">
         <v>1</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ13" t="n">
         <v>1.54</v>
@@ -4184,7 +4184,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ17" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -4620,7 +4620,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR19" t="n">
         <v>0</v>
@@ -5925,7 +5925,7 @@
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ25" t="n">
         <v>0.58</v>
@@ -8541,10 +8541,10 @@
         <v>3</v>
       </c>
       <c r="AP37" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ37" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="AR37" t="n">
         <v>2.08</v>
@@ -9631,7 +9631,7 @@
         <v>2</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ42" t="n">
         <v>1.58</v>
@@ -10070,7 +10070,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR44" t="n">
         <v>1.87</v>
@@ -10288,7 +10288,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR45" t="n">
         <v>1.66</v>
@@ -12686,7 +12686,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ56" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR56" t="n">
         <v>1.89</v>
@@ -13340,7 +13340,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ59" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="AR59" t="n">
         <v>1.19</v>
@@ -13555,7 +13555,7 @@
         <v>2</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ60" t="n">
         <v>1.46</v>
@@ -13773,7 +13773,7 @@
         <v>2.33</v>
       </c>
       <c r="AP61" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ61" t="n">
         <v>1.58</v>
@@ -15302,7 +15302,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ68" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="AR68" t="n">
         <v>0.87</v>
@@ -16607,7 +16607,7 @@
         <v>1.5</v>
       </c>
       <c r="AP74" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ74" t="n">
         <v>1.33</v>
@@ -18136,7 +18136,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ81" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR81" t="n">
         <v>1.35</v>
@@ -18351,7 +18351,7 @@
         <v>2.5</v>
       </c>
       <c r="AP82" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ82" t="n">
         <v>1.82</v>
@@ -19880,7 +19880,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ89" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="AR89" t="n">
         <v>1.99</v>
@@ -20534,7 +20534,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ92" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR92" t="n">
         <v>2.4</v>
@@ -21621,7 +21621,7 @@
         <v>1</v>
       </c>
       <c r="AP97" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ97" t="n">
         <v>0.62</v>
@@ -23801,7 +23801,7 @@
         <v>1.8</v>
       </c>
       <c r="AP107" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ107" t="n">
         <v>1.33</v>
@@ -24022,7 +24022,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ108" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="AR108" t="n">
         <v>2.09</v>
@@ -24458,7 +24458,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ110" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="AR110" t="n">
         <v>1.52</v>
@@ -25112,7 +25112,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ113" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR113" t="n">
         <v>1.27</v>
@@ -25327,7 +25327,7 @@
         <v>0.83</v>
       </c>
       <c r="AP114" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ114" t="n">
         <v>0.67</v>
@@ -27071,7 +27071,7 @@
         <v>1.5</v>
       </c>
       <c r="AP122" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ122" t="n">
         <v>1.46</v>
@@ -28600,7 +28600,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ129" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="AR129" t="n">
         <v>1.89</v>
@@ -29033,7 +29033,7 @@
         <v>0.67</v>
       </c>
       <c r="AP131" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ131" t="n">
         <v>0.83</v>
@@ -30998,7 +30998,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ140" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR140" t="n">
         <v>0.95</v>
@@ -32085,7 +32085,7 @@
         <v>1</v>
       </c>
       <c r="AP145" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ145" t="n">
         <v>1.17</v>
@@ -32521,7 +32521,7 @@
         <v>1.43</v>
       </c>
       <c r="AP147" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ147" t="n">
         <v>1.45</v>
@@ -32960,7 +32960,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ149" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="AR149" t="n">
         <v>1.62</v>
@@ -35140,7 +35140,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ159" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR159" t="n">
         <v>1.5</v>
@@ -36448,7 +36448,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ165" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="AR165" t="n">
         <v>1.73</v>
@@ -37317,7 +37317,7 @@
         <v>1.22</v>
       </c>
       <c r="AP169" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ169" t="n">
         <v>1.33</v>
@@ -38189,7 +38189,7 @@
         <v>0.7</v>
       </c>
       <c r="AP173" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ173" t="n">
         <v>0.62</v>
@@ -39064,7 +39064,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ177" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR177" t="n">
         <v>1.94</v>
@@ -40805,10 +40805,10 @@
         <v>0.8</v>
       </c>
       <c r="AP185" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ185" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR185" t="n">
         <v>1.59</v>
@@ -41895,7 +41895,7 @@
         <v>0.36</v>
       </c>
       <c r="AP190" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ190" t="n">
         <v>0.31</v>
@@ -43424,7 +43424,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ197" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="AR197" t="n">
         <v>1.99</v>
@@ -43857,7 +43857,7 @@
         <v>0.7</v>
       </c>
       <c r="AP199" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AQ199" t="n">
         <v>1.08</v>
@@ -44078,7 +44078,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ200" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="AR200" t="n">
         <v>1.43</v>
@@ -44293,7 +44293,7 @@
         <v>0.4</v>
       </c>
       <c r="AP201" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ201" t="n">
         <v>0.58</v>
@@ -44732,7 +44732,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ203" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR203" t="n">
         <v>1.97</v>
@@ -48296,6 +48296,442 @@
       </c>
       <c r="BP219" t="n">
         <v>1.55</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="n">
+        <v>219</v>
+      </c>
+      <c r="B220" t="n">
+        <v>8007633</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Netherlands Eredivisie</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="n">
+        <v>46081.61458333334</v>
+      </c>
+      <c r="F220" t="n">
+        <v>25</v>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Heracles</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>PSV</t>
+        </is>
+      </c>
+      <c r="I220" t="n">
+        <v>0</v>
+      </c>
+      <c r="J220" t="n">
+        <v>3</v>
+      </c>
+      <c r="K220" t="n">
+        <v>3</v>
+      </c>
+      <c r="L220" t="n">
+        <v>1</v>
+      </c>
+      <c r="M220" t="n">
+        <v>3</v>
+      </c>
+      <c r="N220" t="n">
+        <v>4</v>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>['80']</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>['9', '12', '40']</t>
+        </is>
+      </c>
+      <c r="Q220" t="n">
+        <v>7</v>
+      </c>
+      <c r="R220" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="S220" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="T220" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="U220" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="V220" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="W220" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="X220" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="Y220" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z220" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="AA220" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AB220" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC220" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD220" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE220" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF220" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AG220" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH220" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AI220" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ220" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK220" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AL220" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM220" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AN220" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AO220" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AP220" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AQ220" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AR220" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AS220" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AT220" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="AU220" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV220" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW220" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX220" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY220" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ220" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA220" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB220" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC220" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD220" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE220" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BF220" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BG220" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH220" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="BI220" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BJ220" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BK220" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BL220" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BM220" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BN220" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BO220" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BP220" t="n">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="B221" t="n">
+        <v>8007617</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Netherlands Eredivisie</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="n">
+        <v>46081.70833333334</v>
+      </c>
+      <c r="F221" t="n">
+        <v>25</v>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>NEC</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Fortuna Sittard</t>
+        </is>
+      </c>
+      <c r="I221" t="n">
+        <v>1</v>
+      </c>
+      <c r="J221" t="n">
+        <v>1</v>
+      </c>
+      <c r="K221" t="n">
+        <v>2</v>
+      </c>
+      <c r="L221" t="n">
+        <v>2</v>
+      </c>
+      <c r="M221" t="n">
+        <v>3</v>
+      </c>
+      <c r="N221" t="n">
+        <v>5</v>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>['19', '90+3']</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>['27', '59', '65']</t>
+        </is>
+      </c>
+      <c r="Q221" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R221" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="S221" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="T221" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="U221" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="V221" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="W221" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="X221" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y221" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z221" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA221" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB221" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC221" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD221" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE221" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF221" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AG221" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH221" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AI221" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ221" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AK221" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AL221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM221" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AN221" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AO221" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AP221" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AQ221" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AR221" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS221" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AT221" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AU221" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV221" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW221" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX221" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY221" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ221" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA221" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB221" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC221" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD221" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BE221" t="n">
+        <v>12</v>
+      </c>
+      <c r="BF221" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="BG221" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH221" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI221" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BJ221" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BK221" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BL221" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BM221" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BN221" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BO221" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BP221" t="n">
+        <v>1.53</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Netherlands Eredivisie_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Netherlands Eredivisie_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP221"/>
+  <dimension ref="A1:BP226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,7 +914,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ7" t="n">
         <v>1.33</v>
@@ -2222,7 +2222,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ10" t="n">
         <v>0.31</v>
@@ -3091,10 +3091,10 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -3748,7 +3748,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ17" t="n">
         <v>2.77</v>
@@ -4399,10 +4399,10 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR18" t="n">
         <v>0</v>
@@ -5056,7 +5056,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR21" t="n">
         <v>2.91</v>
@@ -5707,7 +5707,7 @@
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ24" t="n">
         <v>1</v>
@@ -6579,10 +6579,10 @@
         <v>1</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR28" t="n">
         <v>1.04</v>
@@ -6800,7 +6800,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR29" t="n">
         <v>1.94</v>
@@ -7233,7 +7233,7 @@
         <v>1.5</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ31" t="n">
         <v>1.33</v>
@@ -7672,7 +7672,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR33" t="n">
         <v>1.52</v>
@@ -7887,7 +7887,7 @@
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ34" t="n">
         <v>1.08</v>
@@ -8108,7 +8108,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR35" t="n">
         <v>1.55</v>
@@ -8977,7 +8977,7 @@
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ39" t="n">
         <v>0.58</v>
@@ -9413,7 +9413,7 @@
         <v>1.5</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ41" t="n">
         <v>1.46</v>
@@ -9634,7 +9634,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR42" t="n">
         <v>1.46</v>
@@ -9849,10 +9849,10 @@
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR43" t="n">
         <v>1.89</v>
@@ -10721,7 +10721,7 @@
         <v>0</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ47" t="n">
         <v>1</v>
@@ -11593,10 +11593,10 @@
         <v>1</v>
       </c>
       <c r="AP51" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR51" t="n">
         <v>0.9</v>
@@ -11814,7 +11814,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR52" t="n">
         <v>2.56</v>
@@ -12250,7 +12250,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR54" t="n">
         <v>1.27</v>
@@ -12683,7 +12683,7 @@
         <v>1</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ56" t="n">
         <v>0.85</v>
@@ -13119,7 +13119,7 @@
         <v>1.33</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ58" t="n">
         <v>0.62</v>
@@ -13337,7 +13337,7 @@
         <v>3</v>
       </c>
       <c r="AP59" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ59" t="n">
         <v>2.77</v>
@@ -13776,7 +13776,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ61" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR61" t="n">
         <v>2.12</v>
@@ -13991,7 +13991,7 @@
         <v>0</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ62" t="n">
         <v>1.17</v>
@@ -14212,7 +14212,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR63" t="n">
         <v>1.52</v>
@@ -14430,7 +14430,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ64" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR64" t="n">
         <v>1.95</v>
@@ -14648,7 +14648,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ65" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR65" t="n">
         <v>1.61</v>
@@ -14866,7 +14866,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR66" t="n">
         <v>1.08</v>
@@ -15299,7 +15299,7 @@
         <v>3</v>
       </c>
       <c r="AP68" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ68" t="n">
         <v>2.77</v>
@@ -15735,7 +15735,7 @@
         <v>0</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ70" t="n">
         <v>0.31</v>
@@ -16825,7 +16825,7 @@
         <v>0.5</v>
       </c>
       <c r="AP75" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ75" t="n">
         <v>0.42</v>
@@ -17046,7 +17046,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ76" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR76" t="n">
         <v>2.39</v>
@@ -17264,7 +17264,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ77" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR77" t="n">
         <v>1.97</v>
@@ -18133,7 +18133,7 @@
         <v>0.75</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ81" t="n">
         <v>0.85</v>
@@ -18354,7 +18354,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ82" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR82" t="n">
         <v>1.64</v>
@@ -18790,7 +18790,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ84" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR84" t="n">
         <v>1.76</v>
@@ -19223,7 +19223,7 @@
         <v>0</v>
       </c>
       <c r="AP86" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ86" t="n">
         <v>0.31</v>
@@ -19441,7 +19441,7 @@
         <v>1</v>
       </c>
       <c r="AP87" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ87" t="n">
         <v>1.54</v>
@@ -19659,10 +19659,10 @@
         <v>1</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ88" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR88" t="n">
         <v>2.12</v>
@@ -20970,7 +20970,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ94" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR94" t="n">
         <v>1.63</v>
@@ -21842,7 +21842,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR98" t="n">
         <v>1.29</v>
@@ -22275,7 +22275,7 @@
         <v>1</v>
       </c>
       <c r="AP100" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ100" t="n">
         <v>1.54</v>
@@ -22493,7 +22493,7 @@
         <v>0.6</v>
       </c>
       <c r="AP101" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ101" t="n">
         <v>0.83</v>
@@ -22711,7 +22711,7 @@
         <v>0</v>
       </c>
       <c r="AP102" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ102" t="n">
         <v>0.31</v>
@@ -22929,7 +22929,7 @@
         <v>0.4</v>
       </c>
       <c r="AP103" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ103" t="n">
         <v>0.58</v>
@@ -23365,7 +23365,7 @@
         <v>1.8</v>
       </c>
       <c r="AP105" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ105" t="n">
         <v>1.46</v>
@@ -23583,10 +23583,10 @@
         <v>1.4</v>
       </c>
       <c r="AP106" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ106" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR106" t="n">
         <v>1.67</v>
@@ -23804,7 +23804,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ107" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR107" t="n">
         <v>1.79</v>
@@ -24240,7 +24240,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ109" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR109" t="n">
         <v>1.66</v>
@@ -24891,7 +24891,7 @@
         <v>1.33</v>
       </c>
       <c r="AP112" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ112" t="n">
         <v>1.33</v>
@@ -25330,7 +25330,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ114" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR114" t="n">
         <v>1.61</v>
@@ -25548,7 +25548,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR115" t="n">
         <v>1.82</v>
@@ -26417,7 +26417,7 @@
         <v>0.83</v>
       </c>
       <c r="AP119" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ119" t="n">
         <v>1.17</v>
@@ -26635,7 +26635,7 @@
         <v>0.33</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ120" t="n">
         <v>0.58</v>
@@ -27510,7 +27510,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ124" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR124" t="n">
         <v>1.82</v>
@@ -27943,10 +27943,10 @@
         <v>1.86</v>
       </c>
       <c r="AP126" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ126" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR126" t="n">
         <v>2.24</v>
@@ -28164,7 +28164,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ127" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR127" t="n">
         <v>1.85</v>
@@ -28379,10 +28379,10 @@
         <v>1.29</v>
       </c>
       <c r="AP128" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ128" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR128" t="n">
         <v>1.24</v>
@@ -28818,7 +28818,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR130" t="n">
         <v>1.64</v>
@@ -29469,7 +29469,7 @@
         <v>1.29</v>
       </c>
       <c r="AP133" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ133" t="n">
         <v>1.33</v>
@@ -29690,7 +29690,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ134" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR134" t="n">
         <v>1.91</v>
@@ -29905,7 +29905,7 @@
         <v>1.14</v>
       </c>
       <c r="AP135" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ135" t="n">
         <v>1.54</v>
@@ -30995,7 +30995,7 @@
         <v>0.57</v>
       </c>
       <c r="AP140" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ140" t="n">
         <v>0.85</v>
@@ -31434,7 +31434,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ142" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR142" t="n">
         <v>1.82</v>
@@ -31649,10 +31649,10 @@
         <v>0.75</v>
       </c>
       <c r="AP143" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ143" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR143" t="n">
         <v>2.05</v>
@@ -32303,7 +32303,7 @@
         <v>0.75</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ146" t="n">
         <v>0.62</v>
@@ -32524,7 +32524,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ147" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR147" t="n">
         <v>1.78</v>
@@ -32957,7 +32957,7 @@
         <v>3</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ149" t="n">
         <v>2.77</v>
@@ -33178,7 +33178,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ150" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR150" t="n">
         <v>1.58</v>
@@ -33611,7 +33611,7 @@
         <v>1.29</v>
       </c>
       <c r="AP152" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ152" t="n">
         <v>1.46</v>
@@ -33832,7 +33832,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ153" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR153" t="n">
         <v>1.75</v>
@@ -34265,7 +34265,7 @@
         <v>0.67</v>
       </c>
       <c r="AP155" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ155" t="n">
         <v>0.62</v>
@@ -34922,7 +34922,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ158" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR158" t="n">
         <v>1.82</v>
@@ -35358,7 +35358,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ160" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR160" t="n">
         <v>1.68</v>
@@ -35794,7 +35794,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ162" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR162" t="n">
         <v>1.79</v>
@@ -36009,10 +36009,10 @@
         <v>1.44</v>
       </c>
       <c r="AP163" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ163" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR163" t="n">
         <v>0.96</v>
@@ -36227,7 +36227,7 @@
         <v>1</v>
       </c>
       <c r="AP164" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ164" t="n">
         <v>0.83</v>
@@ -36884,7 +36884,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ167" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR167" t="n">
         <v>1.82</v>
@@ -37099,7 +37099,7 @@
         <v>0.75</v>
       </c>
       <c r="AP168" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ168" t="n">
         <v>1.08</v>
@@ -38625,7 +38625,7 @@
         <v>0.89</v>
       </c>
       <c r="AP175" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ175" t="n">
         <v>1</v>
@@ -38846,7 +38846,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ176" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR176" t="n">
         <v>1.6</v>
@@ -39279,7 +39279,7 @@
         <v>1.67</v>
       </c>
       <c r="AP178" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ178" t="n">
         <v>1.46</v>
@@ -40151,7 +40151,7 @@
         <v>1</v>
       </c>
       <c r="AP182" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ182" t="n">
         <v>0.83</v>
@@ -40372,7 +40372,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ183" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR183" t="n">
         <v>1.42</v>
@@ -40587,10 +40587,10 @@
         <v>1.56</v>
       </c>
       <c r="AP184" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ184" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR184" t="n">
         <v>1.31</v>
@@ -41026,7 +41026,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ186" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR186" t="n">
         <v>2.27</v>
@@ -41459,10 +41459,10 @@
         <v>0.7</v>
       </c>
       <c r="AP188" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ188" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR188" t="n">
         <v>1.36</v>
@@ -42113,7 +42113,7 @@
         <v>0.2</v>
       </c>
       <c r="AP191" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ191" t="n">
         <v>0.42</v>
@@ -42331,7 +42331,7 @@
         <v>1.22</v>
       </c>
       <c r="AP192" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ192" t="n">
         <v>1.17</v>
@@ -42767,10 +42767,10 @@
         <v>1.7</v>
       </c>
       <c r="AP194" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ194" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR194" t="n">
         <v>1.68</v>
@@ -42988,7 +42988,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ195" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR195" t="n">
         <v>1.84</v>
@@ -44075,7 +44075,7 @@
         <v>3</v>
       </c>
       <c r="AP200" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AQ200" t="n">
         <v>2.77</v>
@@ -44511,10 +44511,10 @@
         <v>1.45</v>
       </c>
       <c r="AP202" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ202" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR202" t="n">
         <v>1.31</v>
@@ -45168,7 +45168,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ205" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="AR205" t="n">
         <v>2.13</v>
@@ -46909,10 +46909,10 @@
         <v>1.45</v>
       </c>
       <c r="AP213" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ213" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AR213" t="n">
         <v>2.21</v>
@@ -47345,7 +47345,7 @@
         <v>0.58</v>
       </c>
       <c r="AP215" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AQ215" t="n">
         <v>0.62</v>
@@ -48732,6 +48732,1096 @@
       </c>
       <c r="BP221" t="n">
         <v>1.53</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="n">
+        <v>221</v>
+      </c>
+      <c r="B222" t="n">
+        <v>8007390</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Netherlands Eredivisie</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="n">
+        <v>46082.34375</v>
+      </c>
+      <c r="F222" t="n">
+        <v>25</v>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>PEC Zwolle</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Ajax</t>
+        </is>
+      </c>
+      <c r="I222" t="n">
+        <v>0</v>
+      </c>
+      <c r="J222" t="n">
+        <v>0</v>
+      </c>
+      <c r="K222" t="n">
+        <v>0</v>
+      </c>
+      <c r="L222" t="n">
+        <v>0</v>
+      </c>
+      <c r="M222" t="n">
+        <v>0</v>
+      </c>
+      <c r="N222" t="n">
+        <v>0</v>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q222" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="R222" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S222" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T222" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U222" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V222" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="W222" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X222" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Y222" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z222" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA222" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AB222" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AC222" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD222" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE222" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF222" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AG222" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AH222" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AI222" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AJ222" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AK222" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AL222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM222" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN222" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO222" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AP222" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ222" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR222" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AS222" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AT222" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AU222" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV222" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW222" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX222" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY222" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ222" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA222" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB222" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC222" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD222" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE222" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF222" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BG222" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH222" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="BI222" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BJ222" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BK222" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BL222" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BM222" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BN222" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BO222" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="BP222" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="n">
+        <v>222</v>
+      </c>
+      <c r="B223" t="n">
+        <v>8007616</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Netherlands Eredivisie</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="n">
+        <v>46082.4375</v>
+      </c>
+      <c r="F223" t="n">
+        <v>25</v>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Twente</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Feyenoord</t>
+        </is>
+      </c>
+      <c r="I223" t="n">
+        <v>1</v>
+      </c>
+      <c r="J223" t="n">
+        <v>0</v>
+      </c>
+      <c r="K223" t="n">
+        <v>1</v>
+      </c>
+      <c r="L223" t="n">
+        <v>2</v>
+      </c>
+      <c r="M223" t="n">
+        <v>0</v>
+      </c>
+      <c r="N223" t="n">
+        <v>2</v>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>['45+1', '72']</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q223" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R223" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S223" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T223" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U223" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="V223" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="W223" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X223" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y223" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z223" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AA223" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AB223" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AC223" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD223" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE223" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF223" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AG223" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AH223" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AI223" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ223" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AK223" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL223" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM223" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AN223" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO223" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AP223" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AQ223" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR223" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AS223" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AT223" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AU223" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV223" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW223" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX223" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY223" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ223" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA223" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB223" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC223" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD223" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BE223" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="BF223" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BG223" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH223" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="BI223" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BJ223" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BK223" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BL223" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BM223" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BN223" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BO223" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP223" t="n">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="n">
+        <v>223</v>
+      </c>
+      <c r="B224" t="n">
+        <v>8007455</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Netherlands Eredivisie</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="n">
+        <v>46082.4375</v>
+      </c>
+      <c r="F224" t="n">
+        <v>25</v>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Volendam</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Groningen</t>
+        </is>
+      </c>
+      <c r="I224" t="n">
+        <v>1</v>
+      </c>
+      <c r="J224" t="n">
+        <v>1</v>
+      </c>
+      <c r="K224" t="n">
+        <v>2</v>
+      </c>
+      <c r="L224" t="n">
+        <v>3</v>
+      </c>
+      <c r="M224" t="n">
+        <v>2</v>
+      </c>
+      <c r="N224" t="n">
+        <v>5</v>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>['45+7', '56', '90+6']</t>
+        </is>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>['16', '90+2']</t>
+        </is>
+      </c>
+      <c r="Q224" t="n">
+        <v>4</v>
+      </c>
+      <c r="R224" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S224" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T224" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="U224" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V224" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W224" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X224" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y224" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z224" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA224" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB224" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC224" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD224" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="AE224" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF224" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AG224" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH224" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI224" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AJ224" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AK224" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL224" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM224" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN224" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AO224" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AP224" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AQ224" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AR224" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AS224" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AT224" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AU224" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV224" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW224" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX224" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY224" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ224" t="n">
+        <v>28</v>
+      </c>
+      <c r="BA224" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB224" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC224" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD224" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="BE224" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF224" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BG224" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH224" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BI224" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BJ224" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="BK224" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BL224" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM224" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BN224" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO224" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BP224" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="n">
+        <v>224</v>
+      </c>
+      <c r="B225" t="n">
+        <v>8007632</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Netherlands Eredivisie</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="n">
+        <v>46082.53125</v>
+      </c>
+      <c r="F225" t="n">
+        <v>25</v>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Utrecht</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="I225" t="n">
+        <v>2</v>
+      </c>
+      <c r="J225" t="n">
+        <v>0</v>
+      </c>
+      <c r="K225" t="n">
+        <v>2</v>
+      </c>
+      <c r="L225" t="n">
+        <v>2</v>
+      </c>
+      <c r="M225" t="n">
+        <v>0</v>
+      </c>
+      <c r="N225" t="n">
+        <v>2</v>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>['9', '35']</t>
+        </is>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q225" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R225" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="S225" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T225" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U225" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="V225" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="W225" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X225" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="Y225" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z225" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA225" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB225" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AC225" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD225" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE225" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF225" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AG225" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH225" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AI225" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ225" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AK225" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AL225" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM225" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN225" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO225" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AP225" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AQ225" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR225" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AS225" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AT225" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="AU225" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV225" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW225" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX225" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY225" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ225" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA225" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB225" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC225" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD225" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BE225" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF225" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BG225" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH225" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI225" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BJ225" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BK225" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BL225" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BM225" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BN225" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BO225" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BP225" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="n">
+        <v>225</v>
+      </c>
+      <c r="B226" t="n">
+        <v>8007468</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Netherlands Eredivisie</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="n">
+        <v>46082.66666666666</v>
+      </c>
+      <c r="F226" t="n">
+        <v>25</v>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Excelsior</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Go Ahead Eagles</t>
+        </is>
+      </c>
+      <c r="I226" t="n">
+        <v>0</v>
+      </c>
+      <c r="J226" t="n">
+        <v>0</v>
+      </c>
+      <c r="K226" t="n">
+        <v>0</v>
+      </c>
+      <c r="L226" t="n">
+        <v>0</v>
+      </c>
+      <c r="M226" t="n">
+        <v>1</v>
+      </c>
+      <c r="N226" t="n">
+        <v>1</v>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>['54']</t>
+        </is>
+      </c>
+      <c r="Q226" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R226" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="S226" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="T226" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="U226" t="n">
+        <v>3</v>
+      </c>
+      <c r="V226" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="W226" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X226" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="Y226" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z226" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AA226" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AB226" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="AC226" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD226" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE226" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF226" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AG226" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH226" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AI226" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ226" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AK226" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL226" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM226" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AN226" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AO226" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AP226" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AQ226" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AR226" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AS226" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AT226" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AU226" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV226" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW226" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX226" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY226" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ226" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA226" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB226" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC226" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD226" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BE226" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF226" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BG226" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BH226" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BI226" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BJ226" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BK226" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BL226" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BM226" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BN226" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BO226" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BP226" t="n">
+        <v>1.42</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Netherlands Eredivisie_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Netherlands Eredivisie_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP226"/>
+  <dimension ref="A1:BP228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ14" t="n">
         <v>1.17</v>
@@ -3748,7 +3748,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -6361,7 +6361,7 @@
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ27" t="n">
         <v>0.31</v>
@@ -6582,7 +6582,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR28" t="n">
         <v>1.04</v>
@@ -10939,7 +10939,7 @@
         <v>1.5</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ48" t="n">
         <v>0.83</v>
@@ -11814,7 +11814,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR52" t="n">
         <v>2.56</v>
@@ -14209,7 +14209,7 @@
         <v>2.33</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ63" t="n">
         <v>1.67</v>
@@ -14866,7 +14866,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR66" t="n">
         <v>1.08</v>
@@ -17915,7 +17915,7 @@
         <v>1.5</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ80" t="n">
         <v>1.46</v>
@@ -19662,7 +19662,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ88" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR88" t="n">
         <v>2.12</v>
@@ -22057,7 +22057,7 @@
         <v>1.4</v>
       </c>
       <c r="AP99" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ99" t="n">
         <v>1.33</v>
@@ -23586,7 +23586,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ106" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR106" t="n">
         <v>1.67</v>
@@ -26199,7 +26199,7 @@
         <v>0.83</v>
       </c>
       <c r="AP118" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ118" t="n">
         <v>0.62</v>
@@ -28818,7 +28818,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR130" t="n">
         <v>1.64</v>
@@ -30559,7 +30559,7 @@
         <v>0.29</v>
       </c>
       <c r="AP138" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ138" t="n">
         <v>0.42</v>
@@ -32524,7 +32524,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ147" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR147" t="n">
         <v>1.78</v>
@@ -34701,7 +34701,7 @@
         <v>0.25</v>
       </c>
       <c r="AP157" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ157" t="n">
         <v>0.58</v>
@@ -35358,7 +35358,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ160" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR160" t="n">
         <v>1.68</v>
@@ -39061,7 +39061,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP177" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ177" t="n">
         <v>0.85</v>
@@ -40590,7 +40590,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ184" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR184" t="n">
         <v>1.31</v>
@@ -42988,7 +42988,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ195" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR195" t="n">
         <v>1.84</v>
@@ -43421,7 +43421,7 @@
         <v>3</v>
       </c>
       <c r="AP197" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ197" t="n">
         <v>2.77</v>
@@ -44947,7 +44947,7 @@
         <v>0.91</v>
       </c>
       <c r="AP204" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AQ204" t="n">
         <v>1.08</v>
@@ -48874,7 +48874,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ222" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR222" t="n">
         <v>1.14</v>
@@ -49822,6 +49822,442 @@
       </c>
       <c r="BP226" t="n">
         <v>1.42</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="n">
+        <v>226</v>
+      </c>
+      <c r="B227" t="n">
+        <v>8007392</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Netherlands Eredivisie</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="n">
+        <v>46087.66666666666</v>
+      </c>
+      <c r="F227" t="n">
+        <v>26</v>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Heracles</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Utrecht</t>
+        </is>
+      </c>
+      <c r="I227" t="n">
+        <v>0</v>
+      </c>
+      <c r="J227" t="n">
+        <v>0</v>
+      </c>
+      <c r="K227" t="n">
+        <v>0</v>
+      </c>
+      <c r="L227" t="n">
+        <v>0</v>
+      </c>
+      <c r="M227" t="n">
+        <v>0</v>
+      </c>
+      <c r="N227" t="n">
+        <v>0</v>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q227" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="R227" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S227" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T227" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U227" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="V227" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="W227" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X227" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="Y227" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z227" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA227" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB227" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC227" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD227" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE227" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AF227" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AG227" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AH227" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AI227" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ227" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK227" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL227" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM227" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN227" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AO227" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AP227" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AQ227" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AR227" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AS227" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AT227" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AU227" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV227" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW227" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX227" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY227" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ227" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA227" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB227" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC227" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD227" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BE227" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF227" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BG227" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BH227" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="BI227" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ227" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BK227" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BL227" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BM227" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BN227" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BO227" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BP227" t="n">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="n">
+        <v>227</v>
+      </c>
+      <c r="B228" t="n">
+        <v>8007635</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Netherlands Eredivisie</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="n">
+        <v>46088.52083333334</v>
+      </c>
+      <c r="F228" t="n">
+        <v>26</v>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Groningen</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Ajax</t>
+        </is>
+      </c>
+      <c r="I228" t="n">
+        <v>1</v>
+      </c>
+      <c r="J228" t="n">
+        <v>1</v>
+      </c>
+      <c r="K228" t="n">
+        <v>2</v>
+      </c>
+      <c r="L228" t="n">
+        <v>3</v>
+      </c>
+      <c r="M228" t="n">
+        <v>1</v>
+      </c>
+      <c r="N228" t="n">
+        <v>4</v>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>['6', '65', '72']</t>
+        </is>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>['30']</t>
+        </is>
+      </c>
+      <c r="Q228" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="R228" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S228" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T228" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="U228" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="V228" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="W228" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="X228" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Y228" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z228" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA228" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB228" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC228" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD228" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE228" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF228" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AG228" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH228" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AI228" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AJ228" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AK228" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL228" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM228" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN228" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AO228" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AP228" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ228" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AR228" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AS228" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AT228" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AU228" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV228" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW228" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX228" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY228" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ228" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA228" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB228" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC228" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD228" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BE228" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BF228" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BG228" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BH228" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI228" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BJ228" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BK228" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BL228" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BM228" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BN228" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BO228" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BP228" t="n">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Netherlands Eredivisie_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Netherlands Eredivisie_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP228"/>
+  <dimension ref="A1:BP230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ6" t="n">
         <v>1.46</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ12" t="n">
         <v>1.67</v>
@@ -3530,7 +3530,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -4402,7 +4402,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR18" t="n">
         <v>0</v>
@@ -5053,7 +5053,7 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ21" t="n">
         <v>1.23</v>
@@ -7015,7 +7015,7 @@
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ30" t="n">
         <v>0.83</v>
@@ -7233,7 +7233,7 @@
         <v>1.5</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ31" t="n">
         <v>1.33</v>
@@ -8108,7 +8108,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR35" t="n">
         <v>1.55</v>
@@ -9198,7 +9198,7 @@
         <v>2.15</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR40" t="n">
         <v>2.04</v>
@@ -9413,7 +9413,7 @@
         <v>1.5</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ41" t="n">
         <v>1.46</v>
@@ -9634,7 +9634,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR42" t="n">
         <v>1.46</v>
@@ -11811,7 +11811,7 @@
         <v>1</v>
       </c>
       <c r="AP52" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ52" t="n">
         <v>1.31</v>
@@ -13337,7 +13337,7 @@
         <v>3</v>
       </c>
       <c r="AP59" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ59" t="n">
         <v>2.77</v>
@@ -13776,7 +13776,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ61" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR61" t="n">
         <v>2.12</v>
@@ -13994,7 +13994,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR62" t="n">
         <v>1.69</v>
@@ -17043,7 +17043,7 @@
         <v>1.25</v>
       </c>
       <c r="AP76" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ76" t="n">
         <v>0.85</v>
@@ -17264,7 +17264,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ77" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR77" t="n">
         <v>1.97</v>
@@ -17700,7 +17700,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR79" t="n">
         <v>1.99</v>
@@ -18133,7 +18133,7 @@
         <v>0.75</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ81" t="n">
         <v>0.85</v>
@@ -20531,7 +20531,7 @@
         <v>0.6</v>
       </c>
       <c r="AP92" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ92" t="n">
         <v>0.85</v>
@@ -20752,7 +20752,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR93" t="n">
         <v>1.95</v>
@@ -21842,7 +21842,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR98" t="n">
         <v>1.29</v>
@@ -22711,7 +22711,7 @@
         <v>0</v>
       </c>
       <c r="AP102" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ102" t="n">
         <v>0.31</v>
@@ -23150,7 +23150,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ104" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR104" t="n">
         <v>1.64</v>
@@ -25548,7 +25548,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR115" t="n">
         <v>1.82</v>
@@ -26420,7 +26420,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ119" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR119" t="n">
         <v>0.91</v>
@@ -26635,7 +26635,7 @@
         <v>0.33</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ120" t="n">
         <v>0.58</v>
@@ -27289,7 +27289,7 @@
         <v>0.33</v>
       </c>
       <c r="AP123" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ123" t="n">
         <v>0.42</v>
@@ -27946,7 +27946,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ126" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR126" t="n">
         <v>2.24</v>
@@ -28379,7 +28379,7 @@
         <v>1.29</v>
       </c>
       <c r="AP128" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ128" t="n">
         <v>1.23</v>
@@ -30777,7 +30777,7 @@
         <v>0.5</v>
       </c>
       <c r="AP139" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ139" t="n">
         <v>0.31</v>
@@ -31216,7 +31216,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ141" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR141" t="n">
         <v>1.32</v>
@@ -32088,7 +32088,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ145" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR145" t="n">
         <v>1.75</v>
@@ -32303,7 +32303,7 @@
         <v>0.75</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ146" t="n">
         <v>0.62</v>
@@ -33832,7 +33832,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ153" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR153" t="n">
         <v>1.75</v>
@@ -34483,7 +34483,7 @@
         <v>1</v>
       </c>
       <c r="AP156" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ156" t="n">
         <v>1</v>
@@ -36012,7 +36012,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ163" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR163" t="n">
         <v>0.96</v>
@@ -36227,7 +36227,7 @@
         <v>1</v>
       </c>
       <c r="AP164" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ164" t="n">
         <v>0.83</v>
@@ -38407,7 +38407,7 @@
         <v>0.33</v>
       </c>
       <c r="AP174" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ174" t="n">
         <v>0.58</v>
@@ -38846,7 +38846,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ176" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR176" t="n">
         <v>1.6</v>
@@ -40587,7 +40587,7 @@
         <v>1.56</v>
       </c>
       <c r="AP184" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ184" t="n">
         <v>1.31</v>
@@ -41023,7 +41023,7 @@
         <v>1.89</v>
       </c>
       <c r="AP186" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ186" t="n">
         <v>1.67</v>
@@ -42334,7 +42334,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ192" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR192" t="n">
         <v>2.11</v>
@@ -43642,7 +43642,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ198" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR198" t="n">
         <v>1.72</v>
@@ -44511,10 +44511,10 @@
         <v>1.45</v>
       </c>
       <c r="AP202" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ202" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR202" t="n">
         <v>1.31</v>
@@ -46255,10 +46255,10 @@
         <v>1.27</v>
       </c>
       <c r="AP210" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="AQ210" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AR210" t="n">
         <v>2.23</v>
@@ -49528,7 +49528,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ225" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AR225" t="n">
         <v>1.66</v>
@@ -49743,7 +49743,7 @@
         <v>0.67</v>
       </c>
       <c r="AP226" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ226" t="n">
         <v>0.85</v>
@@ -50258,6 +50258,442 @@
       </c>
       <c r="BP228" t="n">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="n">
+        <v>228</v>
+      </c>
+      <c r="B229" t="n">
+        <v>8007405</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Netherlands Eredivisie</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="n">
+        <v>46088.66666666666</v>
+      </c>
+      <c r="F229" t="n">
+        <v>26</v>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>PSV</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="I229" t="n">
+        <v>1</v>
+      </c>
+      <c r="J229" t="n">
+        <v>1</v>
+      </c>
+      <c r="K229" t="n">
+        <v>2</v>
+      </c>
+      <c r="L229" t="n">
+        <v>2</v>
+      </c>
+      <c r="M229" t="n">
+        <v>1</v>
+      </c>
+      <c r="N229" t="n">
+        <v>3</v>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>['45', '86']</t>
+        </is>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>['13']</t>
+        </is>
+      </c>
+      <c r="Q229" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R229" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="S229" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="T229" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="U229" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="V229" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="W229" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="X229" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Y229" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z229" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AA229" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AB229" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AC229" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD229" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE229" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF229" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AG229" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH229" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AI229" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ229" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AK229" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AL229" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM229" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN229" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AO229" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AP229" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AQ229" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR229" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AS229" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AT229" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AU229" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV229" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW229" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX229" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY229" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ229" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA229" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB229" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC229" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD229" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BE229" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF229" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BG229" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BH229" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="BI229" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BJ229" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="BK229" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BL229" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="BM229" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BN229" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BO229" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BP229" t="n">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="B230" t="n">
+        <v>8007400</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Netherlands Eredivisie</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="n">
+        <v>46088.70833333334</v>
+      </c>
+      <c r="F230" t="n">
+        <v>26</v>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Excelsior</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Heerenveen</t>
+        </is>
+      </c>
+      <c r="I230" t="n">
+        <v>0</v>
+      </c>
+      <c r="J230" t="n">
+        <v>1</v>
+      </c>
+      <c r="K230" t="n">
+        <v>1</v>
+      </c>
+      <c r="L230" t="n">
+        <v>1</v>
+      </c>
+      <c r="M230" t="n">
+        <v>2</v>
+      </c>
+      <c r="N230" t="n">
+        <v>3</v>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>['74']</t>
+        </is>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>['38', '67']</t>
+        </is>
+      </c>
+      <c r="Q230" t="n">
+        <v>3</v>
+      </c>
+      <c r="R230" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S230" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="T230" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U230" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="V230" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="W230" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X230" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y230" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z230" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA230" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB230" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AC230" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD230" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE230" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF230" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AG230" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AH230" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AI230" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AJ230" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AK230" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AL230" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM230" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AN230" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AO230" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AP230" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ230" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AR230" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AS230" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AT230" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AU230" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV230" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW230" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX230" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY230" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ230" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA230" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB230" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC230" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD230" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE230" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="BF230" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BG230" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH230" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="BI230" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BJ230" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BK230" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BL230" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BM230" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BN230" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BO230" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BP230" t="n">
+        <v>1.41</v>
       </c>
     </row>
   </sheetData>
